--- a/reports_excel/張希慈個人自評_【主管評下屬用】.xlsx
+++ b/reports_excel/張希慈個人自評_【主管評下屬用】.xlsx
@@ -197,9 +197,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -255,6 +252,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -699,19 +699,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -729,13 +721,13 @@
           <t>在任務交付時完整說明背景脈絡後，交由部屬做出最終決定的主導權，像是在決定策展時，會清楚說明目的以後，讓品牌部門決定哪樣的方案最適合。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -753,13 +745,13 @@
           <t>會保持意識自己的位置與個性都比較容易主動表達不同觀點，因此會特意請主管協助我讓比較難表達意見的成員更有機會表達意見與想法，比如特意在討論改變理論的會議中加入「邀請尚未發言的成員」可以發言的角色（VVN）。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -777,13 +769,13 @@
           <t>整個NPO EAP的方案即是一種嘗試、修正與反思的過程，過程會有一些錯誤的判斷（比如高估NPO成員對於心理諮商服務的使用率），但有立刻發現後討論修正的方法（比如讓單一使用者從三次使用額度補助調高到六次）。以及積極從方案中獲取使用者的意見，比如當了解有人比較不會使用牌卡，立刻討論明年的規劃是否要拿掉免費贈送的模式，改成補助的模式，減少捐贈資源的浪費。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -801,18 +793,18 @@
           <t>當知道 VVN 懷孕時，第一時間選擇讓她改成全遠端，減少懷孕風險，儘管在新人上任時期，也仍選擇尋找兼顧新兵上任的指導需求與讓主管可以安心懷孕的平衡（透過VVN主動有意識與ROO協作共同擔負指導責任）。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【執行長】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$執行長】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -854,7 +846,7 @@
       </c>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>策略決策與組織方向設定</t>
         </is>
@@ -878,19 +870,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>組織治理與財務風險管理</t>
         </is>
@@ -915,19 +907,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>關鍵利害關係人關係建立與維繫</t>
         </is>
@@ -951,19 +943,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>公關、演講與媒體關係</t>
         </is>
@@ -991,19 +983,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>核心團隊培養與組織文化建立</t>
         </is>
@@ -1027,166 +1019,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -1231,7 +1228,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：張希慈（執行長） ｜ 直屬主管：董事會 ｜ 同儕填答樣本：0 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：張希慈（執行長） ｜ 直屬主管：董事會 ｜ 同儕填答樣本：$0 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1292,12 +1289,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -1307,34 +1304,34 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -1344,34 +1341,34 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -1381,34 +1378,34 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -1418,34 +1415,34 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -1455,34 +1452,34 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -1492,22 +1489,22 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1529,22 +1526,22 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1566,22 +1563,22 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1603,22 +1600,22 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1640,22 +1637,22 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1677,22 +1674,22 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1714,34 +1711,34 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -1751,22 +1748,22 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2152,142 +2149,142 @@
       <c r="G39" s="5" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
